--- a/enhancements/test-files/09_ARR_pc0101_2026_JanJun_revised.xlsx
+++ b/enhancements/test-files/09_ARR_pc0101_2026_JanJun_revised.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,16 +548,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8744.08</v>
+        <v>24448.9</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45878</v>
+        <v>45927</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2933.87</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1408.26</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1525.61</v>
       </c>
     </row>
     <row r="3">
@@ -529,12 +596,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,16 +610,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>15521.3</v>
+        <v>13046.43</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45979</v>
+        <v>45771</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46038</v>
+        <v>46040</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1565.57</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1080.24</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P3" t="n">
+        <v>485.33</v>
       </c>
     </row>
     <row r="4">
@@ -566,12 +658,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -580,16 +672,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5416.85</v>
+        <v>8164.23</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46044</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45945</v>
+        <v>45935</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46039</v>
+        <v>46043</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>979.71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>460.46</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P4" t="n">
+        <v>519.25</v>
       </c>
     </row>
     <row r="5">
@@ -603,12 +720,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,17 +734,42 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19163.97</v>
+        <v>7414.17</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46047</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45843</v>
+        <v>46008</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>46046</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>613.89</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P5" t="n">
+        <v>275.81</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -640,12 +782,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,16 +796,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12364.62</v>
+        <v>7922.37</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45800</v>
+        <v>46035</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46067</v>
+        <v>46069</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>950.6799999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>608.4400000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>342.24</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +849,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -691,16 +858,41 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>18297.6</v>
+        <v>15528.67</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45842</v>
+        <v>45933</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46068</v>
+        <v>46072</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1863.44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>801.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1062.16</v>
       </c>
     </row>
     <row r="8">
@@ -714,7 +906,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -728,16 +920,41 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2479.92</v>
+        <v>9535.459999999999</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46075</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46038</v>
+        <v>45932</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1144.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>617.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P8" t="n">
+        <v>526.36</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +973,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -765,16 +982,41 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21336.12</v>
+        <v>5772.39</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46075</v>
+        <v>46076</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>692.6900000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>290.93</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="P9" t="n">
+        <v>401.76</v>
       </c>
     </row>
     <row r="10">
@@ -788,12 +1030,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -802,16 +1044,41 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14846.84</v>
+        <v>3643.97</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45980</v>
+        <v>46036</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46092</v>
+        <v>46096</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>437.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>214.27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="P10" t="n">
+        <v>223.01</v>
       </c>
     </row>
     <row r="11">
@@ -825,7 +1092,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -839,16 +1106,41 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4624.35</v>
+        <v>23857.96</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45911</v>
+        <v>45828</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2862.96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1860.92</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1002.04</v>
       </c>
     </row>
     <row r="12">
@@ -862,12 +1154,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -876,16 +1168,41 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2774.42</v>
+        <v>9638.93</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45823</v>
+        <v>45963</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46099</v>
+        <v>46103</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1156.67</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>763.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>393.27</v>
       </c>
     </row>
     <row r="13">
@@ -899,12 +1216,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -913,16 +1230,41 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8295.02</v>
+        <v>14257.6</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45896</v>
+        <v>45851</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46105</v>
+        <v>46106</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1710.91</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>855.46</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P13" t="n">
+        <v>855.46</v>
       </c>
     </row>
     <row r="14">
@@ -936,12 +1278,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -950,16 +1292,41 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2098.09</v>
+        <v>21012.36</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46063</v>
+        <v>45853</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46128</v>
+        <v>46124</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2521.48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1689.39</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="P14" t="n">
+        <v>832.09</v>
       </c>
     </row>
     <row r="15">
@@ -973,12 +1340,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -987,16 +1354,41 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9886.73</v>
+        <v>20516.79</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45990</v>
+        <v>46041</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46127</v>
+        <v>46131</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2462.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1378.73</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1083.28</v>
       </c>
     </row>
     <row r="16">
@@ -1010,7 +1402,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1024,16 +1416,41 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18405.96</v>
+        <v>19529.73</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45932</v>
+        <v>46066</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46131</v>
+        <v>46130</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2343.57</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1570.19</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="P16" t="n">
+        <v>773.38</v>
       </c>
     </row>
     <row r="17">
@@ -1047,12 +1464,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1061,16 +1478,41 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7246.92</v>
+        <v>21616.73</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45952</v>
+        <v>45981</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2594.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1219.18</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1374.83</v>
       </c>
     </row>
     <row r="18">
@@ -1084,12 +1526,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1098,16 +1540,41 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16540.15</v>
+        <v>6308.92</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46007</v>
+        <v>45979</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46155</v>
+        <v>46158</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>757.0700000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>461.81</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P18" t="n">
+        <v>295.26</v>
       </c>
     </row>
     <row r="19">
@@ -1121,12 +1588,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1135,16 +1602,41 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1462.96</v>
+        <v>4999.44</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46138</v>
+        <v>46064</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>599.9299999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>407.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="P19" t="n">
+        <v>191.98</v>
       </c>
     </row>
     <row r="20">
@@ -1158,12 +1650,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1172,16 +1664,41 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21744.38</v>
+        <v>22183.46</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46059</v>
+        <v>45926</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46164</v>
+        <v>46162</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2662.02</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1810.17</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>851.85</v>
       </c>
     </row>
     <row r="21">
@@ -1195,12 +1712,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1209,16 +1726,41 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19009.08</v>
+        <v>3896.73</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46011</v>
+        <v>46107</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>467.61</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>294.59</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="P21" t="n">
+        <v>173.02</v>
       </c>
     </row>
     <row r="22">
@@ -1232,12 +1774,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1246,17 +1788,42 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8805.700000000001</v>
+        <v>1788.29</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46189</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45977</v>
+        <v>45925</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>46185</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>214.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>96.56999999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P22" t="n">
+        <v>118.02</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1274,7 +1841,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1283,16 +1850,41 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11883.52</v>
+        <v>16518.65</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45997</v>
+        <v>46074</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46191</v>
+        <v>46188</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1982.24</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1169.52</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="P23" t="n">
+        <v>812.72</v>
       </c>
     </row>
     <row r="24">
@@ -1306,12 +1898,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1320,16 +1912,41 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15911.74</v>
+        <v>11745.17</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45989</v>
+        <v>46025</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46192</v>
+        <v>46195</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1409.42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>676.52</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="P24" t="n">
+        <v>732.9</v>
       </c>
     </row>
     <row r="25">
@@ -1343,12 +1960,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1357,16 +1974,41 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10858.2</v>
+        <v>15127.01</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46169</v>
+        <v>46086</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46194</v>
+        <v>46198</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1815.24</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1016.53</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P25" t="n">
+        <v>798.71</v>
       </c>
     </row>
   </sheetData>
